--- a/Assets/Excels/wave data.xlsx
+++ b/Assets/Excels/wave data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris WebOffice" lastEdited="6" lowestEdited="6" rupBuild=""/>
+  <fileVersion appName="Polaris WebOffice" lastEdited="4" lowestEdited="4" rupBuild=""/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
@@ -15,33 +15,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>EnemyType</t>
+    <t>waveCount</t>
   </si>
   <si>
-    <t>SpawnCount</t>
+    <t>EnemyID</t>
   </si>
   <si>
-    <t>SpawnRate</t>
+    <t>Count</t>
   </si>
   <si>
-    <t>EnemyPrefab</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>ZombiePrefab</t>
-  </si>
-  <si>
-    <t>BossPrefab</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>Boss_zombie</t>
+    <t>int</t>
   </si>
 </sst>
 </file>
@@ -81,12 +66,6 @@
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
       <color rgb="FFFF0000"/>
     </font>
     <font>
@@ -179,6 +158,12 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -518,164 +503,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -697,6 +673,7 @@
     <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
     <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
     <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="강조색1" xfId="24" builtinId="29"/>
     <cellStyle name="강조색2" xfId="28" builtinId="33"/>
     <cellStyle name="강조색3" xfId="32" builtinId="37"/>
@@ -707,14 +684,14 @@
     <cellStyle name="계산" xfId="17" builtinId="22"/>
     <cellStyle name="나쁨" xfId="22" builtinId="27"/>
     <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
     <cellStyle name="보통" xfId="23" builtinId="28"/>
     <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
     <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
     <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
     <cellStyle name="요약" xfId="20" builtinId="25"/>
     <cellStyle name="입력" xfId="15" builtinId="20"/>
     <cellStyle name="제목" xfId="10" builtinId="15"/>
@@ -724,10 +701,9 @@
     <cellStyle name="제목4" xfId="14" builtinId="19"/>
     <cellStyle name="좋음" xfId="21" builtinId="26"/>
     <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -1017,101 +993,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
-  <cols>
-    <col min="1" max="1" width="18.25499916" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" width="24.25499916" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" width="20.00499916" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" width="21.12999916" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" width="16.00500011" customWidth="1" outlineLevel="0"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="0">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C4" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2">
+    <row r="5" spans="1:3">
+      <c r="A5" s="0">
+        <v>2</v>
+      </c>
+      <c r="B5" s="0">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C5" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="0">
+        <v>2</v>
+      </c>
+      <c r="B6" s="0">
+        <v>3</v>
+      </c>
+      <c r="C6" s="0">
         <v>4</v>
       </c>
-      <c r="C2" s="2">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="0">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0">
+        <v>2</v>
+      </c>
+      <c r="C7" s="0">
         <v>5</v>
       </c>
-      <c r="D2" s="3">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="0">
+        <v>3</v>
+      </c>
+      <c r="B8" s="0">
+        <v>4</v>
+      </c>
+      <c r="C8" s="0">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Excels/wave data.xlsx
+++ b/Assets/Excels/wave data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris WebOffice" lastEdited="4" lowestEdited="4" rupBuild=""/>
+  <fileVersion appName="Polaris WebOffice" lastEdited="6" lowestEdited="6" rupBuild=""/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
@@ -15,18 +15,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>waveCount</t>
+    <t>EnemyType</t>
   </si>
   <si>
-    <t>EnemyID</t>
+    <t>SpawnCount</t>
   </si>
   <si>
-    <t>Count</t>
+    <t>SpawnRate</t>
   </si>
   <si>
-    <t>int</t>
+    <t>EnemyPrefab</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>ZombiePrefab</t>
+  </si>
+  <si>
+    <t>BossPrefab</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>Boss_zombie</t>
   </si>
 </sst>
 </file>
@@ -66,6 +81,12 @@
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FFFF0000"/>
     </font>
     <font>
@@ -158,12 +179,6 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -503,6 +518,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -518,140 +539,143 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -673,7 +697,6 @@
     <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
     <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
     <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="강조색1" xfId="24" builtinId="29"/>
     <cellStyle name="강조색2" xfId="28" builtinId="33"/>
     <cellStyle name="강조색3" xfId="32" builtinId="37"/>
@@ -684,14 +707,14 @@
     <cellStyle name="계산" xfId="17" builtinId="22"/>
     <cellStyle name="나쁨" xfId="22" builtinId="27"/>
     <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
     <cellStyle name="보통" xfId="23" builtinId="28"/>
     <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
     <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
     <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="요약" xfId="20" builtinId="25"/>
     <cellStyle name="입력" xfId="15" builtinId="20"/>
     <cellStyle name="제목" xfId="10" builtinId="15"/>
@@ -701,9 +724,10 @@
     <cellStyle name="제목4" xfId="14" builtinId="19"/>
     <cellStyle name="좋음" xfId="21" builtinId="26"/>
     <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="2" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -993,96 +1017,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
+  <cols>
+    <col min="1" max="1" width="18.25499916" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" width="24.25499916" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" width="20.00499916" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" width="21.12999916" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" width="16.00500011" customWidth="1" outlineLevel="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0">
-        <v>5</v>
-      </c>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4"/>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>2</v>
-      </c>
-      <c r="C4" s="0">
-        <v>3</v>
-      </c>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4"/>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="0">
-        <v>2</v>
-      </c>
-      <c r="B5" s="0">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0">
-        <v>6</v>
-      </c>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4"/>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="0">
-        <v>2</v>
-      </c>
-      <c r="B6" s="0">
-        <v>3</v>
-      </c>
-      <c r="C6" s="0">
-        <v>4</v>
-      </c>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="0">
-        <v>3</v>
-      </c>
-      <c r="B7" s="0">
-        <v>2</v>
-      </c>
-      <c r="C7" s="0">
-        <v>5</v>
-      </c>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4"/>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="0">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0">
-        <v>4</v>
-      </c>
-      <c r="C8" s="0">
-        <v>2</v>
-      </c>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Excels/wave data.xlsx
+++ b/Assets/Excels/wave data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD50974-B5F9-4063-B11A-390169AEE182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WaveData" sheetId="1" r:id="rId1"/>
@@ -19,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
-  <si>
-    <t>waveCount</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>EnemyID</t>
   </si>
@@ -32,12 +30,24 @@
   <si>
     <t>int</t>
   </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,6 +76,14 @@
       <u/>
       <sz val="11"/>
       <color theme="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -115,10 +133,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -423,95 +447,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3001</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3002</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3003</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>3004</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>3005</v>
+      </c>
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>3006</v>
+      </c>
+      <c r="B8" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
     </row>
